--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,301 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19573000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16635600</v>
+      </c>
+      <c r="F8" s="3">
         <v>15047900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>16161000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13011600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>16381000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>18930900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>16382700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>14341400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>11846800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10192100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>11244800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9250500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>14284900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8243400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>20366300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>11245000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>11279600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>7873000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7192200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6552200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19038000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>16124100</v>
+      </c>
+      <c r="F9" s="3">
         <v>14501900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>15650200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12525500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>15886800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>18440900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>15862700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>13918400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>11481000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>9785200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>10795000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8890800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>13967600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7936200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>20029500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>11002000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>11033500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>7632100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>6959500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>6320500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>511500</v>
+      </c>
+      <c r="F10" s="3">
         <v>546000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>510800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>486100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>494200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>490000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>520000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>423000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>365800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>406900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>449800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>359700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>317300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>307200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>336800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>243000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>246100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>240900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>232700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>231700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +999,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1066,14 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1137,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1113,43 +1152,43 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-23500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3">
-        <v>-6400</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>-6400</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1169,73 +1208,85 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F15" s="3">
         <v>13800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>13100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>12700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>12300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>11700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>9100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>9800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>9700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>8600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>8400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>7200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>4400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>3900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>4400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>3500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>3200</v>
-      </c>
-      <c r="V15" s="3">
-        <v>2900</v>
       </c>
       <c r="W15" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1307,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19477300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16560200</v>
+      </c>
+      <c r="F17" s="3">
         <v>14953400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>16103500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12916000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>16314600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>18860000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>16295300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>14288900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11841900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>10146100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11168500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9223600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>14205000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8194400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>20310200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>11223300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11245500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7851400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>7161300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6527800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>75400</v>
+      </c>
+      <c r="F18" s="3">
         <v>94500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>57500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>95600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>66400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>70900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>87400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>52500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>46000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>76300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>26900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>79900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>49000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>56100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>21700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>34100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>21600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>30900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>24400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1476,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1476,73 +1543,85 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>108300</v>
+        <v>106900</v>
       </c>
       <c r="E21" s="3">
-        <v>70600</v>
+        <v>86800</v>
       </c>
       <c r="F21" s="3">
         <v>108300</v>
       </c>
       <c r="G21" s="3">
+        <v>70600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>108300</v>
+      </c>
+      <c r="I21" s="3">
         <v>78700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>82600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>98700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>61600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>14700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>55700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>84900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>35300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>87100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>53400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>60300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>25600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>38500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>25100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>34100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>27300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,138 +1685,156 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>75400</v>
+      </c>
+      <c r="F23" s="3">
         <v>94500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>57500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>95600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>66400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>70900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>87400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>52500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>76300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>26900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>79900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>49000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>56100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>21700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>34100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>21600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>30900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>24400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F24" s="3">
         <v>25000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>15800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>19000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>14100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>21800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>23400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>10800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>11800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>7400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>12400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>16800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>6900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>7500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>6200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1898,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>50700</v>
+      </c>
+      <c r="F26" s="3">
         <v>69500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>41700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>76600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>52300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>49100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>64000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>41700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>34200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>55300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>19500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>77400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>36600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>39300</v>
-      </c>
-      <c r="R26" s="3">
-        <v>16300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>27200</v>
       </c>
       <c r="T26" s="3">
         <v>16300</v>
       </c>
       <c r="U26" s="3">
+        <v>27200</v>
+      </c>
+      <c r="V26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="W26" s="3">
         <v>23400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>18200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F27" s="3">
         <v>67100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>40200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>74200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>50700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>47600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>62200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>40500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>33100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>53600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>75500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>35700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>38400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>16000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>26700</v>
       </c>
       <c r="T27" s="3">
         <v>16000</v>
       </c>
       <c r="U27" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W27" s="3">
         <v>23000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>17900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2111,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2040,11 +2161,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2058,11 +2179,17 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2253,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2324,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2256,73 +2395,85 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F33" s="3">
         <v>67100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>40200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>74200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>50700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>47600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>62200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>40500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>33100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>53600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>75500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>35700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>38400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>16000</v>
-      </c>
-      <c r="S33" s="3">
-        <v>26700</v>
       </c>
       <c r="T33" s="3">
         <v>16000</v>
       </c>
       <c r="U33" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V33" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W33" s="3">
         <v>23000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>17900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2537,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F35" s="3">
         <v>67100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>40200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>74200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>50700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>47600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>62200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>40500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>33100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>53600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>75500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>35700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>38400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>16000</v>
-      </c>
-      <c r="S35" s="3">
-        <v>26700</v>
       </c>
       <c r="T35" s="3">
         <v>16000</v>
       </c>
       <c r="U35" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W35" s="3">
         <v>23000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>17900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2715,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2742,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1157600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1108300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1401300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1263900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1252100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1108500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1363700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1299700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>983400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1109600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1075600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1001500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1033700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>952600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>465200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>519500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>338900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>471300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>345000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>274400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>358200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,73 +2880,85 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>846400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>708200</v>
+      </c>
+      <c r="F43" s="3">
         <v>723800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>994200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>603000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>583000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>636800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>626100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>550800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>487700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>634100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>494200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>268300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>428000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>411600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>482600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>333700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>427500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>283800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>305600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>352700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,61 +3022,67 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10248700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>9870100</v>
+      </c>
+      <c r="F45" s="3">
         <v>9790100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>10128600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9194900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>10109800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9803900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9486400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>7888100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7567300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6943200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>6464000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>5794000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5550100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>4541900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>4535600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3760400</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
@@ -2896,8 +3093,14 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2961,203 +3164,227 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9864000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>9158600</v>
+      </c>
+      <c r="F47" s="3">
         <v>9046900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>8431100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>7650400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>7054200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>6563400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>8776700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>8819200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>8763700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>7198300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6952300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6020500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>5865600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6061300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4853400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5214000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>5025800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>5141400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5131500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4210700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>264900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>245600</v>
+      </c>
+      <c r="F48" s="3">
         <v>240500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>235400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>235800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>234700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>223600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>222600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>216900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>218600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>221000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>183200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>172500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>163600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>126600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>74600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>76400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>43900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>45700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>45600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>44700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>82400</v>
+      </c>
+      <c r="F49" s="3">
         <v>85200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>88900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>91500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>86200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>90000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>93500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>97200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>100800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>98700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>102500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>106400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>109500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>76300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>73100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>71500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>67900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>65900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>59400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>59300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3448,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3519,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F52" s="3">
         <v>32900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>35500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>40000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>52000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>43000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>41800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>35500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>35100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>37000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>35200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>39300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>36900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>363400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>14000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>18600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3608400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3763200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3248600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3404100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3661,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23244800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21938700</v>
+      </c>
+      <c r="F54" s="3">
         <v>21933100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21918900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19832400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19859600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19408800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>21195700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19229000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18839600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16799800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>15799700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13974800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13474900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>12389500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10870900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>10129300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>9936100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>10054900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>9407700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8710500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3763,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,203 +3790,223 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11036400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10951400</v>
+      </c>
+      <c r="F57" s="3">
         <v>10833600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11240900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9950400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>10951400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10914800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10352900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8678800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8754500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7855900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7347000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6450500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6499100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5050100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5145500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4113200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4013200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3963800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3698100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3629500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6996900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5643900</v>
+      </c>
+      <c r="F58" s="3">
         <v>6122800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5787600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5403500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4385100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3903200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5911600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6838800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6494500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5327900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5514400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4873100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4597400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4990100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3869100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4362400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4233600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4141600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3761200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3270300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>187500</v>
+      </c>
+      <c r="F59" s="3">
         <v>186700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>170300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>171300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>159200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>158900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>169000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>163100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>159800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>168000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>133000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>136900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>141300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>99500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>44800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>47000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>10400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>11300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>9600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3791,96 +4070,108 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>761400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>683100</v>
+      </c>
+      <c r="F61" s="3">
         <v>763900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>901900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>922100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>824200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>847100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>974800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>994700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>755600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>782400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>826900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>887400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>783600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>832700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>459300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>325400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>369900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>507400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>428600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>435400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>8100</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3921,8 +4212,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4283,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4354,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4425,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21762000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>20559600</v>
+      </c>
+      <c r="F66" s="3">
         <v>20603200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20671600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18655800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18789500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>18361500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>20190100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18276000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>17935600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15898400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14939500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13175300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12707400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>11700700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>10222300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9514400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9341900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9484400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8855900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8184500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4527,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4594,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4665,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4736,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4807,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1197200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1128100</v>
+      </c>
+      <c r="F72" s="3">
         <v>1077400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1007900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>966200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>889600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>837300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>788200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>724200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>682500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>675200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>641000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>585700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>572400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>495000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>458400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>419100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>402100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>374900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>358600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>335200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4949,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5020,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +5091,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1482800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1379100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1329900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1247300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1176600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1070100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1047300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1005600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>953000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>904000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>901400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>860200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>799500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>767500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>688800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>648600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>614900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>594200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>570500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>551800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>526000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5233,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F81" s="3">
         <v>67100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>40200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>74200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>50700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>47600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>62200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>40500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>33100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>53600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>75500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>35700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>38400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>16000</v>
-      </c>
-      <c r="S81" s="3">
-        <v>26700</v>
       </c>
       <c r="T81" s="3">
         <v>16000</v>
       </c>
       <c r="U81" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V81" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W81" s="3">
         <v>23000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>17900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5411,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F83" s="3">
         <v>13800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>13100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>12700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>12300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>11700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>9800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>9700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>8600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>8400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>7200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>4400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>3900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>4400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>3500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>3200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>2900</v>
       </c>
       <c r="W83" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5549,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5620,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5691,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5762,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5833,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>371100</v>
+      </c>
+      <c r="F89" s="3">
         <v>207900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1046700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>266500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2702200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>744100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>713600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>783800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-118800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>743400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>37200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>502400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>667600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-130000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>462500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>76100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-213000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5935,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-10300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-11200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-11300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-17000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-8600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-17600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-22400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-11100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6073,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +6144,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-10300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-10800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-17800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-13500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-16800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-10400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-17600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-22800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-226300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-5400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-6900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-23200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-9900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6246,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6313,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6384,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6455,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6526,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-140000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-36200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>88600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-25400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-131000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-19300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>241500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-35000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-47000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-58100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>104500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-146000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>374200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>127800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-43700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-141000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>78600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-7600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>79600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>8100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>14100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-1300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>300</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>300</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>263100</v>
+      </c>
+      <c r="F102" s="3">
         <v>61300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1125600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>223500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2667500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-367500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>697200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>660200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>706700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-23000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>369600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>408400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>621400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>617700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-274800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>518200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>58600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-138300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22106100</v>
+      </c>
+      <c r="E8" s="3">
         <v>19573000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16635600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15047900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16161000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13011600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16381000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18930900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16382700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14341400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11846800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10192100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11244800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9250500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14284900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8243400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20366300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11245000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11279600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7873000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7192200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6552200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21563300</v>
+      </c>
+      <c r="E9" s="3">
         <v>19038000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16124100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14501900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15650200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12525500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15886800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18440900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15862700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13918400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11481000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9785200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10795000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8890800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13967600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7936200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20029500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11002000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11033500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7632100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6959500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6320500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>542800</v>
+      </c>
+      <c r="E10" s="3">
         <v>535000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>511500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>546000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>510800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>486100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>494200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>490000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>520000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>423000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>365800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>406900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>449800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>359700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>317300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>307200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>336800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>243000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>246100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>240900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>232700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>231700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,37 +1160,40 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-6900</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-23500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-6400</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1181,18 +1201,18 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1214,79 +1234,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>11200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22033800</v>
+      </c>
+      <c r="E17" s="3">
         <v>19477300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16560200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14953400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16103500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12916000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16314600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18860000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16295300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14288900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11841900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10146100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11168500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9223600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14205000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8194400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20310200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11223300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11245500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7851400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7161300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6527800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E18" s="3">
         <v>95700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>75400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>94500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>95600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>66400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>70900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>87400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>52500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>79900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>56100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>34100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1549,79 +1583,85 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E21" s="3">
         <v>106900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>86800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>108300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>70600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>108300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>78700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>82600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>98700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>84900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>87100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>53400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>60300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>38500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>25100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>34100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E23" s="3">
         <v>95700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>75400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>95600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>66400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>70900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>87400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>52500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>79900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>56100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>34100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>30900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E24" s="3">
         <v>26600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E26" s="3">
         <v>69100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>69500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>41700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>52300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>49100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>64000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>55300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>77400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>39300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E27" s="3">
         <v>66700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>48900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>67100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>74200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>62200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>40500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>33100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>53600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>38400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2167,8 +2228,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2185,11 +2246,14 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2401,79 +2471,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E33" s="3">
         <v>66700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>48900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>67100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>74200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>62200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>40500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>33100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>53600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>75500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>38400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>23000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E35" s="3">
         <v>66700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>48900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>67100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>74200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>62200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>40500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>33100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>53600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>75500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>38400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>23000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1305100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1157600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1108300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1401300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1263900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1252100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1108500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1363700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1299700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>983400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1109600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1075600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1001500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1033700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>952600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>465200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>519500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>338900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>471300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>345000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>274400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>358200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,79 +2976,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1326300</v>
+      </c>
+      <c r="E43" s="3">
         <v>846400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>708200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>723800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>994200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>603000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>583000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>636800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>626100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>550800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>487700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>634100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>494200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>268300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>428000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>411600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>482600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>333700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>427500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>283800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>305600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>352700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3028,64 +3124,67 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10544900</v>
+      </c>
+      <c r="E45" s="3">
         <v>10248700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9870100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9790100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10128600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9194900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10109800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9803900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9486400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7888100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7567300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6943200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6464000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5794000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5550100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4541900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4535600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3760400</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
@@ -3099,8 +3198,11 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3170,221 +3272,233 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10841700</v>
+      </c>
+      <c r="E47" s="3">
         <v>9864000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9158600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9046900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8431100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7650400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7054200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6563400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8776700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8819200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8763700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7198300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6952300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6020500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5865600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6061300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4853400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5214000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5025800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5141400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5131500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4210700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>280600</v>
+      </c>
+      <c r="E48" s="3">
         <v>264900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>245600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>240500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>235400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>235800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>234700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>223600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>222600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>216900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>218600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>221000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>183200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>172500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>163600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>126600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>74600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>76400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>45600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>44700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E49" s="3">
         <v>80500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>82400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>85200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>88900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>91500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>86200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>90000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>93500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>97200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>100800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>98700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>102500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>106400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>109500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>76300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>73100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>71500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>67900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>65900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>59400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>59300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>405300</v>
+      </c>
+      <c r="E52" s="3">
         <v>37400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>45400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>35500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>52000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>39300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>363400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3608400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3763200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3248600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3404100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25651000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23244800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21938700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21933100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21918900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19832400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19859600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19408800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21195700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19229000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18839600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16799800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15799700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13974800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13474900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12389500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10870900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10129300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9936100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10054900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9407700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8710500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,221 +3922,231 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12048900</v>
+      </c>
+      <c r="E57" s="3">
         <v>11036400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10951400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10833600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11240900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9950400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10951400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10914800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10352900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8678800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8754500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7855900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7347000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6450500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6499100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5050100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5145500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4113200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4013200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3963800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3698100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3629500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7470300</v>
+      </c>
+      <c r="E58" s="3">
         <v>6996900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5643900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6122800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5787600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5403500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4385100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3903200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5911600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6838800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6494500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5327900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5514400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4873100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4597400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4990100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3869100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4362400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4233600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4141600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3761200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3270300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E59" s="3">
         <v>210500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>187500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>186700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>170300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>171300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>159200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>158900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>169000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>163100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>159800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>168000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>133000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>136900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>141300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>99500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>47000</v>
-      </c>
-      <c r="U59" s="3">
-        <v>10400</v>
       </c>
       <c r="V59" s="3">
         <v>10400</v>
       </c>
       <c r="W59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="X59" s="3">
         <v>11300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4076,90 +4216,96 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1139500</v>
+      </c>
+      <c r="E61" s="3">
         <v>761400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>683100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>763900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>901900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>922100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>824200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>847100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>974800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>994700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>755600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>782400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>826900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>887400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>783600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>832700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>459300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>325400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>369900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>507400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>428600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>435400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E62" s="3">
         <v>8800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8100</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
@@ -4173,8 +4319,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24108400</v>
+      </c>
+      <c r="E66" s="3">
         <v>21762000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20559600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20603200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20671600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18655800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18789500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18361500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20190100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18276000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17935600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15898400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14939500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13175300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12707400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11700700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10222300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9514400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9341900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9484400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8855900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8184500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1250300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1197200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1128100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1077400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1007900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>966200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>889600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>837300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>788200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>724200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>682500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>675200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>641000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>585700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>572400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>495000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>458400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>419100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>402100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>374900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>358600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>335200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1542600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1482800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1379100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1329900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1247300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1176600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1070100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1047300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1005600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>953000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>904000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>901400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>860200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>799500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>767500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>688800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>648600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>614900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>594200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>570500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>551800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>526000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E81" s="3">
         <v>66700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>48900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>67100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>74200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>62200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>40500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>33100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>53600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>75500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>38400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>23000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E83" s="3">
         <v>11200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E89" s="3">
         <v>152400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>371100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>207900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1046700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>266500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2702200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>744100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>713600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>783800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-118800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>743400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>37200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>502400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>667600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-130000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>462500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>76100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-213000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-226300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>380100</v>
+      </c>
+      <c r="E100" s="3">
         <v>76900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-81700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-140000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-36200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-131000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>241500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-35000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-47000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-58100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>104500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-146000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>374200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>127800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-43700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-141000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>78600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>79600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1146100</v>
+      </c>
+      <c r="E102" s="3">
         <v>223400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>263100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>61300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1125600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>223500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2667500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-367500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>697200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>660200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>706700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>369600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>408400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>621400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>617700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-274800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>518200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>58600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-138300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27069700</v>
+      </c>
+      <c r="E8" s="3">
         <v>22106100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19573000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16635600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15047900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16161000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13011600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16381000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18930900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16382700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14341400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11846800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10192100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11244800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9250500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14284900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8243400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20366300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11245000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11279600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7873000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7192200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6552200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26477100</v>
+      </c>
+      <c r="E9" s="3">
         <v>21563300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19038000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16124100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14501900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15650200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12525500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15886800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18440900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15862700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13918400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11481000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9785200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10795000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8890800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13967600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7936200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20029500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11002000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11033500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7632100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6959500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6320500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>592600</v>
+      </c>
+      <c r="E10" s="3">
         <v>542800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>535000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>511500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>546000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>510800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>486100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>494200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>490000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>520000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>423000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>365800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>406900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>449800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>359700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>317300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>307200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>336800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>243000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>246100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>240900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>232700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>231700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,40 +1180,43 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-23500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1204,18 +1224,18 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1246,73 +1269,76 @@
         <v>12300</v>
       </c>
       <c r="E15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F15" s="3">
         <v>11200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26981700</v>
+      </c>
+      <c r="E17" s="3">
         <v>22033800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19477300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16560200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14953400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16103500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12916000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16314600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18860000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16295300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14288900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11841900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10146100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11168500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9223600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14205000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8194400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20310200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11223300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11245500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7851400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7161300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6527800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E18" s="3">
         <v>72300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>95700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>75400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>94500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>57500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>95600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>66400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>70900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>87400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>52500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>76300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>79900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>49000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>56100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>34100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1586,82 +1620,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E21" s="3">
         <v>84600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>106900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>86800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>108300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>70600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>108300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>78700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>82600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>98700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>84900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>87100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>53400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>25600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>38500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>34100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>27300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E23" s="3">
         <v>72300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>95700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>75400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>95600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>66400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>70900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>87400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>52500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>46000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>76300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>79900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>49000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>56100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>34100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>30900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E24" s="3">
         <v>19200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E26" s="3">
         <v>53100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>69100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>69500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>52300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>64000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>55300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>77400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>39300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E27" s="3">
         <v>51200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>66700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>48900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>67100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>40200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>74200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>47600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>62200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>40500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>33100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>53600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>38400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>17900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2231,8 +2292,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2249,11 +2310,14 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E33" s="3">
         <v>51200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>66700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>48900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>67100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>40200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>74200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>62200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>40500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>33100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>53600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>38400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>26700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>23000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E35" s="3">
         <v>51200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>66700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>48900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>67100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>40200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>74200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>62200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>40500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>33100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>53600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>38400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>26700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>23000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1220800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1305100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1157600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1108300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1401300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1263900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1252100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1108500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1363700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1299700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>983400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1109600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1075600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1001500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1033700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>952600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>465200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>519500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>338900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>471300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>345000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>274400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>358200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1326300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>846400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>708200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>723800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>994200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>603000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>583000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>636800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>626100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>550800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>487700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>634100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>494200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>268300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>428000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>411600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>482600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>333700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>427500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>283800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>305600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>352700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,67 +3223,70 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10320600</v>
+      </c>
+      <c r="E45" s="3">
         <v>10544900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10248700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9870100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9790100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10128600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9194900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10109800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9803900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9486400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7888100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7567300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6943200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6464000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5794000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5550100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4541900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4535600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3760400</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
@@ -3201,8 +3300,11 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3275,230 +3377,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12215900</v>
+      </c>
+      <c r="E47" s="3">
         <v>10841700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9864000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9158600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9046900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8431100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7650400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7054200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6563400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8776700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8819200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8763700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7198300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6952300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6020500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5865600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6061300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4853400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5214000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5025800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5141400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5131500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4210700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>299600</v>
+      </c>
+      <c r="E48" s="3">
         <v>280600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>264900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>245600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>240500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>235400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>235800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>234700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>223600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>222600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>216900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>218600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>221000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>183200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>172500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>163600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>126600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>74600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>76400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>45700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>45600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>44700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E49" s="3">
         <v>79500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>80500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>82400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>85200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>88900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>91500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>86200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>90000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>93500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>97200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>100800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>98700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>102500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>106400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>109500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>76300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>73100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>71500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>67900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>65900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>59400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>59300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E52" s="3">
         <v>405300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>45400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>52000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>39300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>363400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3608400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3763200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3248600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3404100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25930800</v>
+      </c>
+      <c r="E54" s="3">
         <v>25651000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23244800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21938700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21933100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21918900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19832400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19859600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19408800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21195700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19229000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18839600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16799800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15799700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13974800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13474900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12389500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10870900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10129300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9936100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10054900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9407700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8710500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,230 +4053,240 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11560300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12048900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11036400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10951400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10833600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11240900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9950400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10951400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10914800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10352900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8678800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8754500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7855900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7347000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6450500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6499100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5050100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5145500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4113200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4013200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3963800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3698100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3629500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8195900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7470300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6996900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5643900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6122800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5787600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5403500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4385100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3903200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5911600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6838800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6494500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5327900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5514400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4873100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4597400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4990100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3869100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4362400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4233600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4141600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3761200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3270300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E59" s="3">
         <v>218500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>210500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>187500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>186700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>170300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>171300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>159200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>158900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>169000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>163100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>159800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>168000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>133000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>136900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>141300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>99500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>47000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>10400</v>
       </c>
       <c r="W59" s="3">
         <v>10400</v>
       </c>
       <c r="X59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="Y59" s="3">
         <v>11300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4219,82 +4359,88 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>770600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1139500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>761400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>683100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>763900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>901900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>922100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>824200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>847100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>974800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>994700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>755600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>782400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>826900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>887400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>783600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>832700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>459300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>325400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>369900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>507400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>428600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>435400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4302,13 +4448,13 @@
         <v>8200</v>
       </c>
       <c r="E62" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F62" s="3">
         <v>8800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>8</v>
@@ -4322,8 +4468,8 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24323000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24108400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21762000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20559600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20603200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20671600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18655800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18789500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18361500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20190100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18276000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17935600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15898400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14939500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13175300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12707400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11700700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10222300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9514400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9341900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9484400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8855900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8184500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1312200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1250300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1197200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1128100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1077400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1007900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>966200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>889600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>837300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>788200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>724200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>682500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>675200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>641000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>585700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>572400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>495000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>458400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>419100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>402100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>374900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>358600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>335200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1607800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1542600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1482800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1379100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1329900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1247300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1176600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1070100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1047300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1005600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>953000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>904000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>901400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>860200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>799500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>767500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>688800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>648600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>614900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>594200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>570500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>551800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>526000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E81" s="3">
         <v>51200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>66700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>48900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>67100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>40200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>74200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>62200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>40500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>33100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>53600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>38400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>26700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>23000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5621,73 +5820,76 @@
         <v>12300</v>
       </c>
       <c r="E83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F83" s="3">
         <v>11200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-622100</v>
+      </c>
+      <c r="E89" s="3">
         <v>784000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>152400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>371100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>207900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1046700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>266500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2702200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>744100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>713600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>783800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-118800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>743400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>37200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>502400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>667600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-130000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>462500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>76100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-213000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-226300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-382800</v>
+      </c>
+      <c r="E100" s="3">
         <v>380100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>76900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-81700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-140000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>88600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-131000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>241500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-35000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-47000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>104500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-146000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>374200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>127800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-141000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>78600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>79600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1032900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1146100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>223400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>263100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>61300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1125600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>223500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2667500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-367500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>697200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>660200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>706700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>369600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>408400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>621400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>617700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-274800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>518200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>58600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-138300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>27069700</v>
+        <v>30801200</v>
       </c>
       <c r="E8" s="3">
-        <v>22106100</v>
+        <v>26748600</v>
       </c>
       <c r="F8" s="3">
-        <v>19573000</v>
+        <v>21830700</v>
       </c>
       <c r="G8" s="3">
-        <v>16635600</v>
+        <v>19323800</v>
       </c>
       <c r="H8" s="3">
-        <v>15047900</v>
+        <v>16369100</v>
       </c>
       <c r="I8" s="3">
-        <v>16161000</v>
+        <v>14817000</v>
       </c>
       <c r="J8" s="3">
+        <v>15967400</v>
+      </c>
+      <c r="K8" s="3">
         <v>13011600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16381000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18930900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16382700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14341400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11846800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10192100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11244800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9250500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14284900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8243400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20366300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11245000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11279600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7873000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7192200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>26477100</v>
+        <v>30376700</v>
       </c>
       <c r="E9" s="3">
-        <v>21563300</v>
+        <v>26309000</v>
       </c>
       <c r="F9" s="3">
-        <v>19038000</v>
+        <v>21437200</v>
       </c>
       <c r="G9" s="3">
-        <v>16124100</v>
+        <v>18930200</v>
       </c>
       <c r="H9" s="3">
-        <v>14501900</v>
+        <v>15994000</v>
       </c>
       <c r="I9" s="3">
-        <v>15650200</v>
+        <v>14409100</v>
       </c>
       <c r="J9" s="3">
+        <v>15593700</v>
+      </c>
+      <c r="K9" s="3">
         <v>12525500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15886800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18440900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15862700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13918400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11481000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9785200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10795000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8890800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13967600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7936200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20029500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11002000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11033500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7632100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6959500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>592600</v>
+        <v>424500</v>
       </c>
       <c r="E10" s="3">
-        <v>542800</v>
+        <v>439600</v>
       </c>
       <c r="F10" s="3">
-        <v>535000</v>
+        <v>393500</v>
       </c>
       <c r="G10" s="3">
-        <v>511500</v>
+        <v>393600</v>
       </c>
       <c r="H10" s="3">
-        <v>546000</v>
+        <v>375100</v>
       </c>
       <c r="I10" s="3">
-        <v>510800</v>
+        <v>407900</v>
       </c>
       <c r="J10" s="3">
+        <v>373700</v>
+      </c>
+      <c r="K10" s="3">
         <v>486100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>494200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>490000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>520000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>423000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>365800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>406900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>449800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>359700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>317300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>307200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>336800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>243000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>246100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>240900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>232700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>231700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,61 +1200,64 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-1800</v>
+        <v>1400</v>
       </c>
       <c r="E14" s="3">
-        <v>-6900</v>
+        <v>2300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1900</v>
+        <v>-5800</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J14" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K14" s="3">
         <v>-23500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-6400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1260,85 +1280,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12300</v>
+        <v>17300</v>
       </c>
       <c r="E15" s="3">
         <v>12300</v>
       </c>
       <c r="F15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="G15" s="3">
         <v>11200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26981700</v>
+        <v>30701700</v>
       </c>
       <c r="E17" s="3">
-        <v>22033800</v>
+        <v>26658300</v>
       </c>
       <c r="F17" s="3">
-        <v>19477300</v>
+        <v>21764200</v>
       </c>
       <c r="G17" s="3">
-        <v>16560200</v>
+        <v>19228100</v>
       </c>
       <c r="H17" s="3">
-        <v>14953400</v>
+        <v>16294100</v>
       </c>
       <c r="I17" s="3">
-        <v>16103500</v>
+        <v>14721800</v>
       </c>
       <c r="J17" s="3">
+        <v>15897800</v>
+      </c>
+      <c r="K17" s="3">
         <v>12916000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16314600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18860000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16295300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14288900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11841900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10146100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11168500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9223600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14205000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8194400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20310200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11223300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11245500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7851400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7161300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>88000</v>
+        <v>99500</v>
       </c>
       <c r="E18" s="3">
-        <v>72300</v>
+        <v>90300</v>
       </c>
       <c r="F18" s="3">
+        <v>66500</v>
+      </c>
+      <c r="G18" s="3">
         <v>95700</v>
       </c>
-      <c r="G18" s="3">
-        <v>75400</v>
-      </c>
       <c r="H18" s="3">
-        <v>94500</v>
+        <v>75000</v>
       </c>
       <c r="I18" s="3">
-        <v>57500</v>
+        <v>95200</v>
       </c>
       <c r="J18" s="3">
+        <v>69600</v>
+      </c>
+      <c r="K18" s="3">
         <v>95600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>87400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>52500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>76300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>79900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>49000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>56100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,31 +1579,32 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1623,108 +1657,114 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>100300</v>
+        <v>116800</v>
       </c>
       <c r="E21" s="3">
-        <v>84600</v>
+        <v>102600</v>
       </c>
       <c r="F21" s="3">
+        <v>78800</v>
+      </c>
+      <c r="G21" s="3">
         <v>106900</v>
       </c>
-      <c r="G21" s="3">
-        <v>86800</v>
-      </c>
       <c r="H21" s="3">
+        <v>86200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>109000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>82700</v>
+      </c>
+      <c r="K21" s="3">
         <v>108300</v>
       </c>
-      <c r="I21" s="3">
-        <v>70600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>108300</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>78700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>82600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>98700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>84900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>87100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>53400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>60300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>25600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>25100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>34100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>27300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E23" s="3">
         <v>88000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>72300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>95700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>75400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>57500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>95600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>66400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>70900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>87400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>52500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>46000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>76300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>79900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>49000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>56100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>34100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>30900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E24" s="3">
         <v>26100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E26" s="3">
         <v>61900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>53100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>69100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>69500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>52300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>64000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>41700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>55300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>77400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>36600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>39300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>16300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E27" s="3">
         <v>59700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>51200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>66700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>48900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>40200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>74200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>47600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>62200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>40500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>33100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>53600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>75500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>38400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>23000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2295,8 +2356,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2313,11 +2374,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,31 +2537,34 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2547,85 +2617,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>59700</v>
+        <v>76700</v>
       </c>
       <c r="E33" s="3">
-        <v>51200</v>
+        <v>61900</v>
       </c>
       <c r="F33" s="3">
-        <v>66700</v>
+        <v>53100</v>
       </c>
       <c r="G33" s="3">
-        <v>48900</v>
+        <v>69100</v>
       </c>
       <c r="H33" s="3">
-        <v>67100</v>
+        <v>50700</v>
       </c>
       <c r="I33" s="3">
-        <v>40200</v>
+        <v>69500</v>
       </c>
       <c r="J33" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K33" s="3">
         <v>74200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>62200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>40500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>33100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>53600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>75500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>38400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>23000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>59700</v>
+        <v>76700</v>
       </c>
       <c r="E35" s="3">
-        <v>51200</v>
+        <v>61900</v>
       </c>
       <c r="F35" s="3">
-        <v>66700</v>
+        <v>53100</v>
       </c>
       <c r="G35" s="3">
-        <v>48900</v>
+        <v>69100</v>
       </c>
       <c r="H35" s="3">
-        <v>67100</v>
+        <v>50700</v>
       </c>
       <c r="I35" s="3">
-        <v>40200</v>
+        <v>69500</v>
       </c>
       <c r="J35" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K35" s="3">
         <v>74200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>62200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>40500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>33100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>53600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>75500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>38400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>23000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,108 +3004,112 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1269000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1220800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1305100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1157600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1108300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1401300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1263900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1252100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1108500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1363700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1299700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>983400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1109600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1075600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1001500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1033700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>952600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>465200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>519500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>338900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>471300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>345000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>274400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>358200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>16472100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>14966300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>13680100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>12633300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>11579700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>11534000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>10938300</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3072,108 +3162,114 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>900300</v>
+        <v>8315600</v>
       </c>
       <c r="E43" s="3">
-        <v>1326300</v>
+        <v>8470500</v>
       </c>
       <c r="F43" s="3">
-        <v>846400</v>
+        <v>9032800</v>
       </c>
       <c r="G43" s="3">
-        <v>708200</v>
+        <v>8325800</v>
       </c>
       <c r="H43" s="3">
-        <v>723800</v>
+        <v>8157200</v>
       </c>
       <c r="I43" s="3">
-        <v>994200</v>
+        <v>8026800</v>
       </c>
       <c r="J43" s="3">
+        <v>8615600</v>
+      </c>
+      <c r="K43" s="3">
         <v>603000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>583000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>636800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>626100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>550800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>487700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>634100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>494200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>268300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>428000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>411600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>482600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>333700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>427500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>283800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>305600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>352700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>681100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>587400</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>616900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>518400</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>537300</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>444700</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>572100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,71 +3322,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10320600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10544900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10248700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9870100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>9790100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>10128600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>9194900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10109800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9803900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9486400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7888100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7567300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6943200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6464000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5794000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5550100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4541900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4535600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3760400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3303,31 +3402,34 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>26737800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>25245000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>24997900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>22635100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>21382500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>21406800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>21389900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3380,239 +3482,251 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>12215900</v>
-      </c>
-      <c r="E47" s="3">
-        <v>10841700</v>
-      </c>
-      <c r="F47" s="3">
-        <v>9864000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>9158600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>9046900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>8431100</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>7650400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7054200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6563400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8776700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8819200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8763700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7198300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6952300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6020500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5865600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6061300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4853400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5214000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5025800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5141400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5131500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300100</v>
+      </c>
+      <c r="E48" s="3">
         <v>299600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>280600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>264900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>245600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>240500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>235400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>235800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>234700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>223600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>222600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>216900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>218600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>221000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>183200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>172500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>163600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>126600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>74600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>76400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>45700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>45600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>44700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E49" s="3">
         <v>77100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>85200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>88900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>91500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>86200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>90000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>93500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>97200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>100800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>98700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>102500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>106400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>109500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>73100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>71500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>67900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>65900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>59400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>59300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>42300</v>
+        <v>301500</v>
       </c>
       <c r="E52" s="3">
-        <v>405300</v>
+        <v>266800</v>
       </c>
       <c r="F52" s="3">
-        <v>37400</v>
+        <v>250700</v>
       </c>
       <c r="G52" s="3">
-        <v>45400</v>
+        <v>226900</v>
       </c>
       <c r="H52" s="3">
-        <v>32900</v>
+        <v>182800</v>
       </c>
       <c r="I52" s="3">
+        <v>167700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>169200</v>
+      </c>
+      <c r="K52" s="3">
+        <v>40000</v>
+      </c>
+      <c r="L52" s="3">
+        <v>52000</v>
+      </c>
+      <c r="M52" s="3">
+        <v>43000</v>
+      </c>
+      <c r="N52" s="3">
+        <v>41800</v>
+      </c>
+      <c r="O52" s="3">
         <v>35500</v>
       </c>
-      <c r="J52" s="3">
-        <v>40000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>52000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>43000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>41800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>35500</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>37000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>39300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>363400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>18600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3608400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3763200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3248600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27466300</v>
+      </c>
+      <c r="E54" s="3">
         <v>25930800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25651000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23244800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21938700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21933100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21918900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19832400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19859600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19408800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21195700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19229000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18839600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16799800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15799700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13974800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13474900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12389500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10870900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10129300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9936100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10054900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9407700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,262 +4184,272 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11597700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11560300</v>
       </c>
-      <c r="E57" s="3">
-        <v>12048900</v>
-      </c>
       <c r="F57" s="3">
-        <v>11036400</v>
+        <v>12047200</v>
       </c>
       <c r="G57" s="3">
+        <v>11034600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>10948000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>10832000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>11239500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>9950400</v>
+      </c>
+      <c r="L57" s="3">
         <v>10951400</v>
       </c>
-      <c r="H57" s="3">
-        <v>10833600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>11240900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>9950400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>10951400</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10914800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10352900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8678800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8754500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7855900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7347000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6450500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6499100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5050100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5145500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4113200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4013200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3963800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3698100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8195900</v>
+        <v>10612200</v>
       </c>
       <c r="E58" s="3">
-        <v>7470300</v>
+        <v>1451600</v>
       </c>
       <c r="F58" s="3">
-        <v>6996900</v>
+        <v>1901000</v>
       </c>
       <c r="G58" s="3">
-        <v>5643900</v>
+        <v>1188200</v>
       </c>
       <c r="H58" s="3">
-        <v>6122800</v>
+        <v>5929600</v>
       </c>
       <c r="I58" s="3">
-        <v>5787600</v>
+        <v>1499900</v>
       </c>
       <c r="J58" s="3">
+        <v>974200</v>
+      </c>
+      <c r="K58" s="3">
         <v>5403500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4385100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3903200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5911600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6838800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6494500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5327900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5514400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4873100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4597400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4990100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3869100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4362400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4233600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4141600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3761200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>218200</v>
+        <v>2608700</v>
       </c>
       <c r="E59" s="3">
-        <v>218500</v>
+        <v>3266700</v>
       </c>
       <c r="F59" s="3">
-        <v>210500</v>
+        <v>2817200</v>
       </c>
       <c r="G59" s="3">
-        <v>187500</v>
+        <v>2543700</v>
       </c>
       <c r="H59" s="3">
-        <v>186700</v>
+        <v>2837000</v>
       </c>
       <c r="I59" s="3">
-        <v>170300</v>
+        <v>2325400</v>
       </c>
       <c r="J59" s="3">
+        <v>2387400</v>
+      </c>
+      <c r="K59" s="3">
         <v>171300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>159200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>158900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>169000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>159800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>168000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>133000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>136900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>141300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>99500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>47000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>10400</v>
       </c>
       <c r="X59" s="3">
         <v>10400</v>
       </c>
       <c r="Y59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="Z59" s="3">
         <v>11300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>24820800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>16278600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>16767100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>14768300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>19716500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>14658900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>14602500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4362,99 +4502,105 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>770600</v>
+        <v>927800</v>
       </c>
       <c r="E61" s="3">
-        <v>1139500</v>
+        <v>8036200</v>
       </c>
       <c r="F61" s="3">
-        <v>761400</v>
+        <v>7333100</v>
       </c>
       <c r="G61" s="3">
-        <v>683100</v>
+        <v>6984900</v>
       </c>
       <c r="H61" s="3">
-        <v>763900</v>
+        <v>835000</v>
       </c>
       <c r="I61" s="3">
-        <v>901900</v>
+        <v>5944300</v>
       </c>
       <c r="J61" s="3">
+        <v>6069100</v>
+      </c>
+      <c r="K61" s="3">
         <v>922100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>824200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>847100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>974800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>994700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>755600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>782400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>826900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>887400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>783600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>832700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>459300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>325400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>369900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>507400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>428600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>435400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>8200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>8200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>8100</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>8</v>
@@ -4471,8 +4617,8 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25757200</v>
+      </c>
+      <c r="E66" s="3">
         <v>24323000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24108400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21762000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20559600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20603200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20671600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18655800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18789500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18361500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20190100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18276000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17935600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15898400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14939500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13175300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12707400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11700700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10222300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9514400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9341900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9484400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8855900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1388900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1312200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1250300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1197200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1128100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1077400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1007900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>966200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>889600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>837300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>788200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>724200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>682500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>675200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>641000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>585700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>572400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>495000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>458400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>419100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>402100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>374900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>358600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>335200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1709100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1607800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1542600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1482800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1379100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1329900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1247300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1176600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1070100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1047300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1005600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>953000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>904000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>901400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>860200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>799500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>767500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>688800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>648600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>614900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>594200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>570500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>551800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>526000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>59700</v>
+        <v>76700</v>
       </c>
       <c r="E81" s="3">
-        <v>51200</v>
+        <v>61900</v>
       </c>
       <c r="F81" s="3">
-        <v>66700</v>
+        <v>53100</v>
       </c>
       <c r="G81" s="3">
-        <v>48900</v>
+        <v>69100</v>
       </c>
       <c r="H81" s="3">
-        <v>67100</v>
+        <v>50700</v>
       </c>
       <c r="I81" s="3">
-        <v>40200</v>
+        <v>69500</v>
       </c>
       <c r="J81" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K81" s="3">
         <v>74200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>62200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>40500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>33100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>53600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>75500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>38400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>23000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>11300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="L83" s="3">
         <v>12300</v>
       </c>
-      <c r="E83" s="3">
-        <v>12300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>11200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>11400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>12700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>12300</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>192600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-622100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>784000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>152400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>371100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>207900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1046700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>266500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2702200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>744100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>713600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>783800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-118800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>743400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>37200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>502400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>667600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-130000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>462500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>76100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-226300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-382800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>380100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>76900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-81700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-140000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>88600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-131000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>241500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-58100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>104500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-146000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>374200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>127800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-141000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>78600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>79600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-9100</v>
+        <v>-12200</v>
       </c>
       <c r="E101" s="3">
-        <v>-4600</v>
+        <v>3700</v>
       </c>
       <c r="F101" s="3">
-        <v>6800</v>
+        <v>3000</v>
       </c>
       <c r="G101" s="3">
-        <v>-12200</v>
+        <v>8100</v>
       </c>
       <c r="H101" s="3">
-        <v>3700</v>
+        <v>-5700</v>
       </c>
       <c r="I101" s="3">
-        <v>3000</v>
+        <v>-5400</v>
       </c>
       <c r="J101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K101" s="3">
         <v>8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>14100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>294300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1146100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>223400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>263100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>61300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1125600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>223500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2667500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-367500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>697200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>660200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>706700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>369600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>408400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>621400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>617700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-274800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>518200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>58600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,365 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27613900</v>
+      </c>
+      <c r="E8" s="3">
         <v>30801200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26748600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21830700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19323800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16369100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14817000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15967400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13011600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16381000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18930900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16382700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14341400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11846800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10192100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11244800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9250500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14284900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8243400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20366300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11245000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11279600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7873000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27152300</v>
+      </c>
+      <c r="E9" s="3">
         <v>30376700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26309000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21437200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18930200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15994000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14409100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15593700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12525500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15886800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18440900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15862700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13918400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11481000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9785200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10795000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8890800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13967600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7936200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20029500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11002000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11033500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7632100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>461600</v>
+      </c>
+      <c r="E10" s="3">
         <v>424500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>439600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>393500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>393600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>375100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>407900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>373700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>486100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>494200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>490000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>520000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>423000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>365800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>406900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>449800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>359700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>317300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>336800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>243000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>246100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>240900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>232700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>231700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,64 +1219,67 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-23500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-6400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1283,88 +1302,94 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E15" s="3">
         <v>17300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>12300</v>
       </c>
       <c r="F15" s="3">
         <v>12300</v>
       </c>
       <c r="G15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H15" s="3">
         <v>11200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27497500</v>
+      </c>
+      <c r="E17" s="3">
         <v>30701700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26658300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21764200</v>
       </c>
-      <c r="G17" s="3">
-        <v>19228100</v>
-      </c>
       <c r="H17" s="3">
+        <v>19226800</v>
+      </c>
+      <c r="I17" s="3">
         <v>16294100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14721800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15897800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12916000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16314600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18860000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16295300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14288900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11841900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10146100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11168500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9223600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14205000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8194400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20310200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11223300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11245500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7851400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E18" s="3">
         <v>99500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>90300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66500</v>
       </c>
-      <c r="G18" s="3">
-        <v>95700</v>
-      </c>
       <c r="H18" s="3">
+        <v>97000</v>
+      </c>
+      <c r="I18" s="3">
         <v>75000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>95200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>69600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>95600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>87400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>52500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>76300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>79900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>49000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>56100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>34100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>21600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>30900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1612,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1597,17 +1630,17 @@
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1660,88 +1693,94 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E21" s="3">
         <v>116800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>102600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78800</v>
       </c>
-      <c r="G21" s="3">
-        <v>106900</v>
-      </c>
       <c r="H21" s="3">
+        <v>108200</v>
+      </c>
+      <c r="I21" s="3">
         <v>86200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>109000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>82700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>108300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>78700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>82600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>98700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>84900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>87100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>53400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>60300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>38500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>25100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>34100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1766,8 +1805,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1820,168 +1859,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E23" s="3">
         <v>98100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>88000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>72300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>95700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>75400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>57500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>95600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>66400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>70900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>87400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>52500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>76300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>26900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>79900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>56100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>34100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>30900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>24400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E24" s="3">
         <v>21400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E26" s="3">
         <v>76700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>61900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>53100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>69100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>69500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>41700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>76600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>52300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>64000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>41700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>34200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>55300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>77400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>39300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>16300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E27" s="3">
         <v>74100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>59700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>66700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>48900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>67100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>40200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>74200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>50700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>47600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>62200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>40500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>53600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>75500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>38400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>16000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2359,8 +2419,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2377,11 +2437,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2606,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2557,17 +2626,17 @@
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2620,88 +2689,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E33" s="3">
         <v>76700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>61900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>53100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>69100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>69500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>41700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>74200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>50700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>47600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>62200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>40500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>53600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>75500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>38400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E35" s="3">
         <v>76700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>61900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>53100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>69100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>69500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>41700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>74200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>50700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>47600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>62200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>40500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>53600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>75500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>38400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,115 +3090,119 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1398200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1269000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1220800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1305100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1157600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1108300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1401300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1263900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1252100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1108500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1363700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1299700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>983400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1109600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1075600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1001500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1033700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>952600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>465200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>519500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>338900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>471300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>345000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>274400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>358200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17674600</v>
+      </c>
+      <c r="E42" s="3">
         <v>16472100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14966300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13680100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12633300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11579700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11534000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10938300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3165,115 +3254,121 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8901100</v>
+      </c>
+      <c r="E43" s="3">
         <v>8315600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8470500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9032800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8325800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8157200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8026800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8615600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>603000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>583000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>636800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>626100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>550800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>487700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>634100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>494200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>268300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>428000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>411600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>482600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>333700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>427500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>283800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>305600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>352700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>861400</v>
+      </c>
+      <c r="E44" s="3">
         <v>681100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>587400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>616900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>518400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>537300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>444700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>572100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -3325,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3351,48 +3449,48 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>9194900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10109800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9803900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9486400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7888100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7567300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6943200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6464000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5794000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5550100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4541900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4535600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3760400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3405,35 +3503,38 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28835300</v>
+      </c>
+      <c r="E46" s="3">
         <v>26737800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25245000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24997900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22635100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21382500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21406800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21389900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3485,8 +3586,11 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3511,222 +3615,231 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>7650400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7054200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6563400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8776700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8819200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8763700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7198300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6952300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6020500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5865600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6061300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4853400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5214000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5025800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5141400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E48" s="3">
         <v>300100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>299600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>280600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>264900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>245600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>240500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>235400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>235800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>234700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>223600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>222600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>216900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>218600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>221000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>183200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>163600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>126600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>74600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>76400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>45700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>45600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>44700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E49" s="3">
         <v>80600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>77100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>80500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>82400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>85200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>88900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>91500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>86200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>90000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>93500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>97200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>100800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>98700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>102500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>106400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>109500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>73100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>71500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>67900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>65900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>59400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>59300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4001,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>304600</v>
+      </c>
+      <c r="E52" s="3">
         <v>301500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>266800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>250700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>226900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>182800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>167700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>169200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>52000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>37000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>39300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>363400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3608400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3763200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29585300</v>
+      </c>
+      <c r="E54" s="3">
         <v>27466300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25930800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25651000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23244800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21938700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21933100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21918900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19832400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19859600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19408800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21195700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19229000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18839600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16799800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15799700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13974800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13474900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12389500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10870900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10129300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9936100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10054900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,275 +4314,285 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11597700</v>
+        <v>12225500</v>
       </c>
       <c r="E57" s="3">
+        <v>11566600</v>
+      </c>
+      <c r="F57" s="3">
         <v>11560300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12047200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11034600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10948000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10832000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11239500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9950400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10951400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10914800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10352900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8678800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8754500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7855900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7347000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6450500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6499100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5050100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5145500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4113200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4013200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3963800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10612200</v>
+        <v>10989200</v>
       </c>
       <c r="E58" s="3">
-        <v>1451600</v>
+        <v>10662900</v>
       </c>
       <c r="F58" s="3">
-        <v>1901000</v>
+        <v>8523500</v>
       </c>
       <c r="G58" s="3">
-        <v>1188200</v>
+        <v>7912700</v>
       </c>
       <c r="H58" s="3">
-        <v>5929600</v>
+        <v>7242400</v>
       </c>
       <c r="I58" s="3">
-        <v>1499900</v>
+        <v>5932200</v>
       </c>
       <c r="J58" s="3">
+        <v>6529400</v>
+      </c>
+      <c r="K58" s="3">
         <v>974200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5403500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4385100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3903200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5911600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6838800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6494500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5327900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5514400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4873100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4597400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4990100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3869100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4362400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4233600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4141600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2608700</v>
+        <v>3285500</v>
       </c>
       <c r="E59" s="3">
+        <v>2639800</v>
+      </c>
+      <c r="F59" s="3">
         <v>3266700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2817200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2543700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2837000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2325400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2387400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>171300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>159200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>158900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>169000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>163100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>159800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>168000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>133000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>136900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>141300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>99500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>47000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>10400</v>
       </c>
       <c r="Y59" s="3">
         <v>10400</v>
       </c>
       <c r="Z59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AA59" s="3">
         <v>11300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>24820800</v>
+        <v>26500200</v>
       </c>
       <c r="E60" s="3">
-        <v>16278600</v>
+        <v>24871500</v>
       </c>
       <c r="F60" s="3">
-        <v>16767100</v>
+        <v>23350500</v>
       </c>
       <c r="G60" s="3">
-        <v>14768300</v>
+        <v>22778800</v>
       </c>
       <c r="H60" s="3">
-        <v>19716500</v>
+        <v>20822500</v>
       </c>
       <c r="I60" s="3">
-        <v>14658900</v>
+        <v>19719100</v>
       </c>
       <c r="J60" s="3">
+        <v>19688400</v>
+      </c>
+      <c r="K60" s="3">
         <v>14602500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4505,88 +4644,94 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>927800</v>
+        <v>1291900</v>
       </c>
       <c r="E61" s="3">
-        <v>8036200</v>
+        <v>877100</v>
       </c>
       <c r="F61" s="3">
-        <v>7333100</v>
+        <v>964300</v>
       </c>
       <c r="G61" s="3">
-        <v>6984900</v>
+        <v>1321400</v>
       </c>
       <c r="H61" s="3">
-        <v>835000</v>
+        <v>930700</v>
       </c>
       <c r="I61" s="3">
-        <v>5944300</v>
+        <v>832400</v>
       </c>
       <c r="J61" s="3">
+        <v>914800</v>
+      </c>
+      <c r="K61" s="3">
         <v>6069100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>922100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>824200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>847100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>974800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>994700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>755600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>782400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>826900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>887400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>783600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>832700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>459300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>325400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>369900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>507400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>428600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>435400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4620,8 +4765,8 @@
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -4665,8 +4810,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27807900</v>
+      </c>
+      <c r="E66" s="3">
         <v>25757200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24323000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24108400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21762000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20559600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20603200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20671600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18655800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18789500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18361500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20190100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18276000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17935600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15898400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14939500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13175300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12707400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11700700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10222300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9514400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9341900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9484400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1388900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1312200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1250300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1197200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1128100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1077400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1007900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>966200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>889600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>837300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>788200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>724200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>682500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>675200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>641000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>585700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>572400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>495000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>458400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>419100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>402100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>374900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>358600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>335200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1777400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1709100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1607800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1542600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1482800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1379100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1329900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1247300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1176600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1070100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1047300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1005600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>953000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>904000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>901400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>860200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>799500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>767500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>688800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>648600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>614900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>594200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>570500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>551800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>526000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E81" s="3">
         <v>76700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>61900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>53100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>69100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>69500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>41700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>74200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>50700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>47600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>62200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>40500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>53600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>75500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>38400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6207,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E83" s="3">
         <v>14700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-477800</v>
+      </c>
+      <c r="E89" s="3">
         <v>192600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-622100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>784000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>152400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>371100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>207900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1046700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>266500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2702200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>744100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>713600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>783800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-118800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>743400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>502400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>667600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-130000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>462500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>76100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6819,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-17600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-226300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7209,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7512,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>188200</v>
+      </c>
+      <c r="E100" s="3">
         <v>113800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-382800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>380100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>76900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-81700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-140000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>88600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-131000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>241500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-47000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-58100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>104500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-146000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>374200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>127800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>78600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>79600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>14100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-329600</v>
+      </c>
+      <c r="E102" s="3">
         <v>294300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1146100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>223400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>263100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>61300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1125600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>223500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2667500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-367500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>697200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>660200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>706700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>369600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>408400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>621400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>617700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-274800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>518200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>58600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36559300</v>
+      </c>
+      <c r="E8" s="3">
         <v>27613900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30801200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26748600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21830700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19323800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16369100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14817000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15967400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13011600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16381000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18930900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16382700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14341400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11846800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10192100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11244800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9250500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14284900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8243400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20366300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11245000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11279600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7873000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36100700</v>
+      </c>
+      <c r="E9" s="3">
         <v>27152300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30376700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26309000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21437200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18930200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15994000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14409100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15593700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12525500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15886800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18440900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15862700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13918400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11481000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9785200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10795000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8890800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13967600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7936200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20029500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11002000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11033500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7632100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>458600</v>
+      </c>
+      <c r="E10" s="3">
         <v>461600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>424500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>439600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>393500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>393600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>375100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>407900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>373700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>486100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>494200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>490000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>520000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>423000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>365800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>406900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>449800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>359700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>317300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>307200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>336800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>243000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>246100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>240900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>232700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>231700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,67 +1239,70 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-5800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-23500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-6400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1305,91 +1325,97 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E15" s="3">
         <v>15700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12300</v>
       </c>
       <c r="G15" s="3">
         <v>12300</v>
       </c>
       <c r="H15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="I15" s="3">
         <v>11200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36460200</v>
+      </c>
+      <c r="E17" s="3">
         <v>27497500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30701700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26658300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21764200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19226800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16294100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14721800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15897800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12916000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16314600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18860000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16295300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14288900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11841900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10146100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11168500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9223600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14205000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8194400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20310200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11223300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11245500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7851400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E18" s="3">
         <v>116400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>99500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>90300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>66500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>97000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>75000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>95200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>69600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>95600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>66400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>87400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>52500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>76300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>79900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>49000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>56100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>34100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>21600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>30900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,8 +1646,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1633,17 +1667,17 @@
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1696,91 +1730,97 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>114700</v>
+      </c>
+      <c r="E21" s="3">
         <v>132100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>116800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>102600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>78800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>108200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>86200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>109000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>82700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>108300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>78700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>82600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>55700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>84900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>35300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>87100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>53400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>60300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>25600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>38500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>34100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1808,8 +1848,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1862,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E23" s="3">
         <v>116900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>98100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>88000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>72300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>95700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>75400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>57500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>95600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>66400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>70900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>87400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>52500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>46000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>76300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>26900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>79900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>49000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>56100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>34100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>30900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E24" s="3">
         <v>31800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>19200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E26" s="3">
         <v>85100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>76700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>61900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>53100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>69100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>69500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>41700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>76600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>52300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>64000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>41700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>34200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>55300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>77400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>39300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>16300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>16300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>23400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E27" s="3">
         <v>82400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>74100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>59700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>66700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>48900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>67100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>40200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>74200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>50700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>47600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>62200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>40500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>53600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>75500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>38400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>23000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2422,8 +2483,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2440,11 +2501,14 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,8 +2676,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2629,17 +2699,17 @@
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2692,91 +2762,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E33" s="3">
         <v>85100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>76700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>61900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>53100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>69100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>69500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>74200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>50700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>47600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>62200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>40500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>53600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>75500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>38400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E35" s="3">
         <v>85100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>76700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>61900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>53100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>69100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>69500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>74200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>50700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>47600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>62200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>40500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>53600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>75500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>38400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,121 +3177,125 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1307300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1398200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1269000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1220800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1305100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1157600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1108300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1401300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1263900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1252100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1108500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1363700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1299700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>983400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1109600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1075600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1001500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1033700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>952600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>465200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>519500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>338900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>471300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>345000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>274400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>358200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19772700</v>
+      </c>
+      <c r="E42" s="3">
         <v>17674600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16472100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14966300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13680100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12633300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11579700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11534000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10938300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3257,121 +3347,127 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8643900</v>
+      </c>
+      <c r="E43" s="3">
         <v>8901100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8315600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8470500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9032800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8325800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8157200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8026800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8615600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>603000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>583000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>636800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>626100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>550800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>487700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>634100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>494200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>268300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>428000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>411600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>482600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>333700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>427500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>283800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>305600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>352700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>796200</v>
+      </c>
+      <c r="E44" s="3">
         <v>861400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>681100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>587400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>616900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>518400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>537300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>444700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>572100</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -3423,8 +3519,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3452,48 +3551,48 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>9194900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10109800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9803900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9486400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7888100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7567300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6943200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6464000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5794000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5550100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4541900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4535600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3760400</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3506,38 +3605,41 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30520100</v>
+      </c>
+      <c r="E46" s="3">
         <v>28835300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26737800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25245000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24997900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22635100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21382500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21406800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21389900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3618,228 +3723,237 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>7650400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7054200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6563400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8776700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8819200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8763700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7198300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6952300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6020500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5865600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6061300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4853400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5214000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5025800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5141400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>306100</v>
+      </c>
+      <c r="E48" s="3">
         <v>304800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>300100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>299600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>280600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>264900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>245600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>240500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>235400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>234700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>223600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>222600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>216900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>218600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>221000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>183200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>172500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>163600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>126600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>76400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>43900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>45700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>45600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>44700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E49" s="3">
         <v>87000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>80600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>77100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>79500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>80500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>82400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>85200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>88900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>91500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>86200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>90000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>93500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>97200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>100800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>98700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>102500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>106400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>109500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>76300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>73100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>71500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>67900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>65900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>59400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>59300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,91 +4121,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>316400</v>
+      </c>
+      <c r="E52" s="3">
         <v>304600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>301500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>266800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>250700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>226900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>182800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>167700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>169200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>52000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>39300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>363400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3608400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3763200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31282900</v>
+      </c>
+      <c r="E54" s="3">
         <v>29585300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27466300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25930800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25651000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23244800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21938700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21933100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21918900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19832400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19859600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19408800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21195700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19229000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18839600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16799800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15799700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13974800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13474900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12389500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10870900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10129300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9936100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10054900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,287 +4445,297 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11822600</v>
+      </c>
+      <c r="E57" s="3">
         <v>12225500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11566600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11560300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12047200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11034600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10948000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10832000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11239500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9950400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10951400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10914800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10352900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8678800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8754500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7855900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7347000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6450500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6499100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5050100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5145500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4113200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4013200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3963800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12852700</v>
+      </c>
+      <c r="E58" s="3">
         <v>10989200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10662900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8523500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7912700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7242400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5932200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6529400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>974200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5403500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4385100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3903200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5911600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6838800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6494500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5327900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5514400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4873100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4597400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4990100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3869100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4362400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4233600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4141600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3614000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3285500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2639800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3266700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2817200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2543700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2837000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2325400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2387400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>171300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>159200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>158900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>169000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>163100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>159800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>168000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>133000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>136900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>141300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>99500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>47000</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>10400</v>
       </c>
       <c r="Z59" s="3">
         <v>10400</v>
       </c>
       <c r="AA59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AB59" s="3">
         <v>11300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28289300</v>
+      </c>
+      <c r="E60" s="3">
         <v>26500200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24871500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23350500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22778800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20822500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19719100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19688400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14602500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4647,91 +4787,97 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1086400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1291900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>877100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>964300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1321400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>930700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>832400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>914800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6069100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>922100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>824200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>847100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>974800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>994700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>755600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>782400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>826900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>887400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>783600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>832700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>459300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>325400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>369900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>507400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>428600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>435400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4768,8 +4914,8 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29400900</v>
+      </c>
+      <c r="E66" s="3">
         <v>27807900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25757200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24323000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24108400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21762000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20559600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20603200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20671600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18655800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18789500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18361500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20190100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18276000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17935600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15898400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14939500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13175300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12707400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11700700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10222300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9514400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9341900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9484400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1545700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1474000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1388900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1312200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1250300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1197200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1128100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1077400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1007900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>966200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>889600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>837300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>788200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>724200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>682500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>675200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>641000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>585700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>572400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>495000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>458400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>419100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>402100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>374900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>358600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>335200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1882000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1777400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1709100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1607800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1542600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1482800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1379100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1329900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1247300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1176600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1070100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1047300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1005600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>953000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>904000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>901400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>860200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>799500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>767500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>688800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>648600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>614900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>594200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>570500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>551800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>526000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E81" s="3">
         <v>85100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>76700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>61900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>53100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>69100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>69500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>74200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>50700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>47600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>62200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>40500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>53600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>75500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>38400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,91 +6406,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E83" s="3">
         <v>12400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-154500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-477800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>192600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-622100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>784000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>152400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>371100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>207900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1046700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>266500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2702200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>744100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>713600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>783800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-118800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>743400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>502400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>667600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-130000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>462500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>76100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,91 +7040,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-226300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7212,8 +7446,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,253 +7758,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-206500</v>
+      </c>
+      <c r="E100" s="3">
         <v>188200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>113800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-382800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>380100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>76900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-81700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-140000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>88600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-131000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>241500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-35000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-47000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-58100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>104500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-146000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>374200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>127800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-43700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-141000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>78600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>79600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>14100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-370400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-329600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>294300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1146100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>223400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>263100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1125600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>223500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2667500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-367500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>697200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>660200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>706700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>369600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>408400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>621400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>617700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-274800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>518200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>58600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34437400</v>
+      </c>
+      <c r="E8" s="3">
         <v>36559300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27613900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30801200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26748600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21830700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19323800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16369100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14817000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15967400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13011600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16381000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18930900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16382700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14341400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11846800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10192100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11244800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9250500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14284900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8243400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20366300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11245000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11279600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7873000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>33980500</v>
+      </c>
+      <c r="E9" s="3">
         <v>36100700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27152300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30376700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26309000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21437200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18930200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15994000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14409100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15593700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12525500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15886800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18440900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15862700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13918400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11481000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9785200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10795000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8890800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13967600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7936200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20029500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11002000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11033500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7632100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E10" s="3">
         <v>458600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>461600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>424500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>439600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>393500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>393600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>375100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>407900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>373700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>486100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>494200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>490000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>520000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>423000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>365800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>406900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>449800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>359700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>317300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>307200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>336800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>243000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>246100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>240900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>232700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>231700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,70 +1259,73 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-5800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-23500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1328,94 +1348,100 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E15" s="3">
         <v>15600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>12300</v>
       </c>
       <c r="H15" s="3">
         <v>12300</v>
       </c>
       <c r="I15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J15" s="3">
         <v>11200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>9700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>7200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34349100</v>
+      </c>
+      <c r="E17" s="3">
         <v>36460200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27497500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30701700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26658300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21764200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19226800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16294100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14721800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15897800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12916000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16314600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18860000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16295300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14288900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11841900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10146100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11168500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9223600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14205000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8194400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20310200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11223300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11245500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7851400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E18" s="3">
         <v>99100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>116400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>99500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>90300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>66500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>97000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>75000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>95200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>69600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>95600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>66400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>87400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>52500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>76300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>79900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>49000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>56100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>21700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>34100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>21600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>30900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1670,17 +1704,17 @@
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1733,94 +1767,100 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E21" s="3">
         <v>114700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>132100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>116800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>102600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>78800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>108200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>86200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>109000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>82700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>108300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>78700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>82600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>98700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>55700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>84900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>35300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>87100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>53400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>60300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>25600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>38500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>25100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>34100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>27300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1851,8 +1891,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E23" s="3">
         <v>97100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>116900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>98100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>88000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>72300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>95700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>75400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>57500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>95600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>66400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>87400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>52500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>46000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>26900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>79900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>49000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>56100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>34100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E24" s="3">
         <v>25400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>24700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E26" s="3">
         <v>71700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>85100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>61900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>53100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>69100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>69500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>76600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>52300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>64000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>41700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>55300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>77400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>36600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>39300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>16300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>16300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E27" s="3">
         <v>69600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>74100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>59700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>66700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>48900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>67100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>40200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>74200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>50700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>47600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>62200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>40500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>53600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>75500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>38400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>16000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>16000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2486,8 +2547,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2504,11 +2565,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2702,17 +2772,17 @@
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2765,94 +2835,100 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E33" s="3">
         <v>71700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>85100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>61900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>53100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>69100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>69500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>50700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>47600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>62200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>40500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>53600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>75500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>38400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E35" s="3">
         <v>71700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>85100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>61900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>53100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>69100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>69500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>50700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>47600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>62200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>40500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>53600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>75500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>38400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,127 +3264,131 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1313100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1307300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1398200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1269000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1220800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1305100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1157600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1108300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1401300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1263900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1252100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1108500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1363700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1299700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>983400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1109600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1075600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1001500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1033700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>952600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>465200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>519500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>338900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>471300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>345000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>274400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>358200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22543700</v>
+      </c>
+      <c r="E42" s="3">
         <v>19772700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17674600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16472100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14966300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13680100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12633300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11579700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11534000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10938300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3350,127 +3440,133 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8891400</v>
+      </c>
+      <c r="E43" s="3">
         <v>8643900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8901100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8315600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8470500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9032800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8325800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8157200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8026800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8615600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>603000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>583000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>636800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>626100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>550800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>487700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>634100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>494200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>268300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>428000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>411600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>482600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>333700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>427500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>283800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>305600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>352700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>705400</v>
+      </c>
+      <c r="E44" s="3">
         <v>796200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>861400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>681100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>587400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>616900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>518400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>537300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>444700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>572100</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3554,48 +3653,48 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>9194900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10109800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9803900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9486400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7888100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7567300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6943200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6464000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5794000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5550100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4541900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4535600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3760400</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3608,41 +3707,44 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33453600</v>
+      </c>
+      <c r="E46" s="3">
         <v>30520100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28835300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26737800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25245000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24997900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22635100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21382500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21406800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21389900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3694,8 +3796,11 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3726,234 +3831,243 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>7650400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7054200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6563400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8776700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8819200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8763700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7198300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6952300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6020500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5865600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6061300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4853400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5214000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5025800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5141400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>310100</v>
+      </c>
+      <c r="E48" s="3">
         <v>306100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>304800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>300100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>299600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>280600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>264900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>245600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>240500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>235800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>234700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>223600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>222600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>216900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>218600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>221000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>183200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>172500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>163600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>126600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>74600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>76400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>43900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>45700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>45600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>44700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E49" s="3">
         <v>90000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>87000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>77100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>79500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>80500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>82400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>85200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>88900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>91500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>86200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>90000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>93500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>97200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>100800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>98700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>102500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>106400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>109500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>73100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>71500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>67900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>65900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>59400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>59300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>373700</v>
+      </c>
+      <c r="E52" s="3">
         <v>316400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>304600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>301500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>266800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>250700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>226900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>182800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>167700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>169200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>37000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>39300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>363400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>18600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3608400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3763200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34265600</v>
+      </c>
+      <c r="E54" s="3">
         <v>31282900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29585300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27466300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25930800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25651000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23244800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21938700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21933100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21918900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19832400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19859600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19408800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21195700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19229000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18839600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16799800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15799700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13974800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13474900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12389500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10870900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10129300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9936100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10054900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,299 +4576,309 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12038900</v>
+      </c>
+      <c r="E57" s="3">
         <v>11822600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12225500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11566600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11560300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12047200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11034600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10948000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10832000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11239500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9950400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10951400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10914800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10352900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8678800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8754500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7855900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7347000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6450500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6499100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5050100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5145500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4113200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4013200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3963800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15615200</v>
+      </c>
+      <c r="E58" s="3">
         <v>12852700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10989200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10662900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8523500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7912700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7242400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5932200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6529400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>974200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5403500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4385100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3903200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5911600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6838800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6494500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5327900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5514400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4873100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4597400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4990100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3869100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4362400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4233600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4141600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3515400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3614000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3285500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2639800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3266700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2817200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2543700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2837000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2325400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2387400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>171300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>159200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>158900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>169000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>163100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>159800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>168000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>133000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>136900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>141300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>99500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>44800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>47000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>10400</v>
       </c>
       <c r="AA59" s="3">
         <v>10400</v>
       </c>
       <c r="AB59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AC59" s="3">
         <v>11300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31169500</v>
+      </c>
+      <c r="E60" s="3">
         <v>28289300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26500200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24871500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23350500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22778800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20822500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19719100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19688400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14602500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4790,94 +4930,100 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1104300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1086400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1291900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>877100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>964300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1321400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>930700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>832400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>914800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6069100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>922100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>824200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>847100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>974800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>994700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>755600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>782400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>826900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>887400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>783600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>832700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>459300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>325400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>369900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>507400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>428600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>435400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4917,8 +5063,8 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32286800</v>
+      </c>
+      <c r="E66" s="3">
         <v>29400900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27807900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25757200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24323000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24108400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21762000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20559600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20603200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20671600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18655800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18789500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18361500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20190100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18276000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17935600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15898400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14939500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13175300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12707400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11700700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10222300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9514400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9341900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9484400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1609100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1545700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1474000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1388900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1312200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1250300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1197200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1128100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1077400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1007900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>966200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>889600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>837300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>788200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>724200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>682500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>675200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>641000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>585700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>572400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>495000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>458400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>419100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>402100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>374900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>358600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>335200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1978800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1882000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1777400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1709100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1607800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1542600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1482800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1379100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1329900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1247300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1176600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1070100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1047300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1005600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>953000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>904000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>901400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>860200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>799500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>767500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>688800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>648600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>614900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>594200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>570500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>551800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>526000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E81" s="3">
         <v>71700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>85100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>61900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>53100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>69100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>69500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>50700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>47600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>62200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>40500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>53600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>75500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>38400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E83" s="3">
         <v>16100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1491200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-154500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-477800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>192600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-622100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>784000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>152400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>371100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>207900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1046700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>266500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2702200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>744100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>713600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>783800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-118800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>743400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>37200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>502400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>667600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-130000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>462500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>76100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-17600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-226300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7449,8 +7683,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-206500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>188200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>113800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-382800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>380100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>76900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-81700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-140000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>88600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-131000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>241500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-35000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-47000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-58100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>104500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-146000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>374200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>127800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>78600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>79600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>14100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-370400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-329600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>294300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1146100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>223400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>263100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>61300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1125600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>223500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2667500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-367500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>697200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>660200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>706700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>369600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>408400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>621400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>617700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-274800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>518200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>58600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,403 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38541900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>32287100</v>
+      </c>
+      <c r="F8" s="3">
         <v>34437400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>36559300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>27613900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>30801200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>26748600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>21830700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>19323800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16369100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>14817000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>15967400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13011600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16381000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>18930900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>16382700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>14341400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>11846800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10192100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11244800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9250500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>14284900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>8243400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>20366300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>11245000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11279600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>7873000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>37858000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>31736800</v>
+      </c>
+      <c r="F9" s="3">
         <v>33980500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>36100700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>27152300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>30376700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>26309000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>21437200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>18930200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>15994000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>14409100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>15593700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>12525500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>15886800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>18440900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>15862700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>13918400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>11481000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>9785200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>10795000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>8890800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>13967600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>7936200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>20029500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11002000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>11033500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>7632100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>683900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>550300</v>
+      </c>
+      <c r="F10" s="3">
         <v>456900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>458600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>461600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>424500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>439600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>393500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>393600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>375100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>407900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>373700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>486100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>494200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>490000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>520000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>423000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>365800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>406900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>449800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>359700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>317300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>307200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>336800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>243000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>246100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>240900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>232700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>231700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,76 +1295,82 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="3">
         <v>2700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>12100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-23500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-6400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1351,97 +1390,109 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F15" s="3">
         <v>14900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>15600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>15700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>17300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>12300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>12300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>11200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>13800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>13100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>12700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>12300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>11700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>11300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>9100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>9800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>9700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>8600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>8400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>7200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>4400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>4200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>3900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>4400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>3500</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>2900</v>
       </c>
       <c r="AE15" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1521,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38354000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>32176700</v>
+      </c>
+      <c r="F17" s="3">
         <v>34349100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>36460200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>27497500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>30701700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>26658300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>21764200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>19226800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16294100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>14721800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>15897800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>12916000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>16314600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>18860000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>16295300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>14288900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11841900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10146100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>11168500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>9223600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>14205000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>8194400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>20310200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>11223300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>11245500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>7851400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>187900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>110400</v>
+      </c>
+      <c r="F18" s="3">
         <v>88300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>99100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>116400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>99500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>90300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>66500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>97000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>75000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>95200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>69600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>95600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>66400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>70900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>87400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>52500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>46000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>76300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>26900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>79900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>49000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>56100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>21700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>34100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>21600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>30900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>24400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1746,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1707,20 +1774,20 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1770,97 +1837,109 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>131700</v>
+      </c>
+      <c r="F21" s="3">
         <v>103200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>114700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>132100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>116800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>102600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>78800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>108200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>86200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>109000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>82700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>108300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>78700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>82600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>98700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>61600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>14700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>55700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>84900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>35300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>87100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>53400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>60300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>25600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>38500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>25100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>34100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>27300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1894,11 +1973,11 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1948,186 +2027,204 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>184900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>109200</v>
+      </c>
+      <c r="F23" s="3">
         <v>85600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>97100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>116900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>98100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>88000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>72300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>95700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>75400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>94500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>57500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>95600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>66400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>70900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>87400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>52500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>46000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>76300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>26900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>79900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>49000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>56100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>21700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>34100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>21600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>30900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>24400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F24" s="3">
         <v>22200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>25400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>31800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>21400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>26100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>19200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>26600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>24700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>25000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>15800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>19000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>14100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>21800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>23400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>10800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>11800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>21000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>7400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>12400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>16800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>5400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>6900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>7500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>6200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F26" s="3">
         <v>63400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>71700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>85100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>76700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>61900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>53100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>69100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>50700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>69500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>41700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>76600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>52300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>49100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>64000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>41700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>7300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>34200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>55300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>19500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>77400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>36600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>39300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>16300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>27200</v>
       </c>
       <c r="AB26" s="3">
         <v>16300</v>
       </c>
       <c r="AC26" s="3">
+        <v>27200</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AE26" s="3">
         <v>23400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>18200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>82600</v>
+      </c>
+      <c r="F27" s="3">
         <v>61000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>69600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>82400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>74100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>59700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>51200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>66700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>48900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>67100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>40200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>74200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>50700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>47600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>62200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>40500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>33100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>53600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>19000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>75500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>35700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>38400</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>16000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>26700</v>
       </c>
       <c r="AB27" s="3">
         <v>16000</v>
       </c>
       <c r="AC27" s="3">
+        <v>26700</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE27" s="3">
         <v>23000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>17900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2550,11 +2671,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2568,11 +2689,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2882,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2775,20 +2914,20 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2838,97 +2977,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F33" s="3">
         <v>63400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>71700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>85100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>76700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>61900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>53100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>69100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>50700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>69500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>41700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>74200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>50700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>47600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>62200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>40500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>33100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>53600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>19000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>75500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>35700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>38400</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>16000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>26700</v>
       </c>
       <c r="AB33" s="3">
         <v>16000</v>
       </c>
       <c r="AC33" s="3">
+        <v>26700</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE33" s="3">
         <v>23000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>17900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F35" s="3">
         <v>63400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>71700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>85100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>76700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>61900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>53100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>69100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>50700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>69500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>41700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>74200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>50700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>47600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>62200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>40500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>33100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>53600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>19000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>75500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>35700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>38400</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>16000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>26700</v>
       </c>
       <c r="AB35" s="3">
         <v>16000</v>
       </c>
       <c r="AC35" s="3">
+        <v>26700</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE35" s="3">
         <v>23000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>17900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,136 +3436,144 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1592700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1605800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1313100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1307300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1398200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1269000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1220800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1305100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1157600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1108300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1401300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1263900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1252100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1108500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1363700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1299700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>983400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1109600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1075600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1001500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1033700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>952600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>465200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>519500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>338900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>471300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>345000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>274400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>358200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>31792000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>26943900</v>
+      </c>
+      <c r="F42" s="3">
         <v>22543700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>19772700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>17674600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>16472100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>14966300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>13680100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>12633300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>11579700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11534000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>10938300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3443,136 +3622,148 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11329000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14270300</v>
+      </c>
+      <c r="F43" s="3">
         <v>8891400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8643900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8901100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8315600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8470500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9032800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8325800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8157200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8026800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8615600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>603000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>583000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>636800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>626100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>550800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>487700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>634100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>494200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>268300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>428000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>411600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>482600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>333700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>427500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>283800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>305600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>352700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1373900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>917500</v>
+      </c>
+      <c r="F44" s="3">
         <v>705400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>796200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>861400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>681100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>587400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>616900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>518400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>537300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>444700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>572100</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -3621,8 +3812,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3656,51 +3853,51 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>9194900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>10109800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>9803900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>9486400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7888100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>7567300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6943200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>6464000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>5794000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>5550100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>4541900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>4535600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3760400</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3710,47 +3907,53 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46087600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>43737500</v>
+      </c>
+      <c r="F46" s="3">
         <v>33453600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>30520100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>28835300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>26737800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>25245000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>24997900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>22635100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21382500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>21406800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21389900</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3799,8 +4002,14 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3834,240 +4043,258 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>7650400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>7054200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6563400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>8776700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>8819200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>8763700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>7198300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6952300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6020500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>5865600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6061300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>4853400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>5214000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5025800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>5141400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>328500</v>
+      </c>
+      <c r="F48" s="3">
         <v>310100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>306100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>304800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>300100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>299600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>280600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>264900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>245600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>240500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>235400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>235800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>234700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>223600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>222600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>216900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>218600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>221000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>183200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>172500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>163600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>126600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>74600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>76400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>43900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>45700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>45600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>44700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>736200</v>
+      </c>
+      <c r="F49" s="3">
         <v>88900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>90000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>87000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>80600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>77100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>79500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>80500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>82400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>85200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>88900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>91500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>86200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>90000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>93500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>97200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>100800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>98700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>102500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>106400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>109500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>76300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>73100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>71500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>67900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>65900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>59400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>59300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4477,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>590200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>433800</v>
+      </c>
+      <c r="F52" s="3">
         <v>373700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>316400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>304600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>301500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>266800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>250700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>226900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>182800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>167700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>169200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>40000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>52000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>43000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>41800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>35500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>35100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>37000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>35200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>39300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>36900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>363400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>14000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>18600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3608400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3763200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47784400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>45268000</v>
+      </c>
+      <c r="F54" s="3">
         <v>34265600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>31282900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29585300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>27466300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>25930800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>25651000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>23244800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21938700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>21933100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>21918900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>19832400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>19859600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>19408800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>21195700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>19229000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>18839600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>16799800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15799700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>13974800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>13474900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>12389500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>10870900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>10129300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>9936100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>10054900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,314 +4836,334 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20830800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>21562300</v>
+      </c>
+      <c r="F57" s="3">
         <v>12038900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11822600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>12225500</v>
       </c>
-      <c r="G57" s="3">
-        <v>11566600</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>11597700</v>
+      </c>
+      <c r="J57" s="3">
         <v>11560300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12047200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11034600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>10948000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10832000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11239500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9950400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>10951400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>10914800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>10352900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>8678800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>8754500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>7855900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>7347000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>6450500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>6499100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5050100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5145500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>4113200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4013200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3963800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18632500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>16697900</v>
+      </c>
+      <c r="F58" s="3">
         <v>15615200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12852700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10989200</v>
       </c>
-      <c r="G58" s="3">
-        <v>10662900</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>10462000</v>
+      </c>
+      <c r="J58" s="3">
         <v>8523500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7912700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7242400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5932200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6529400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>974200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5403500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4385100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3903200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5911600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6838800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>6494500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5327900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5514400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>4873100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4597400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4990100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3869100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4362400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4233600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4141600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3994700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2677600</v>
+      </c>
+      <c r="F59" s="3">
         <v>3515400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3614000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3285500</v>
       </c>
-      <c r="G59" s="3">
-        <v>2639800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>2608900</v>
+      </c>
+      <c r="J59" s="3">
         <v>3266700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2817200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2543700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2837000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2325400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2387400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>171300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>159200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>158900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>169000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>163100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>159800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>168000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>133000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>136900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>141300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>99500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>44800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>47000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>10400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>10400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>11300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>9600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43458000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>40939800</v>
+      </c>
+      <c r="F60" s="3">
         <v>31169500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>28289300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>26500200</v>
       </c>
-      <c r="G60" s="3">
-        <v>24871500</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>24670800</v>
+      </c>
+      <c r="J60" s="3">
         <v>23350500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>22778800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20822500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19719100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19688400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14602500</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4933,97 +5212,109 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1702300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1853900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1104300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1086400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1291900</v>
       </c>
-      <c r="G61" s="3">
-        <v>877100</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>1077800</v>
+      </c>
+      <c r="J61" s="3">
         <v>964300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1321400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>930700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>832400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>914800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6069100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>922100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>824200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>847100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>974800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>994700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>755600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>782400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>826900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>887400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>783600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>832700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>459300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>325400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>369900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>507400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>428600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>435400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5066,11 +5357,11 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -5111,8 +5402,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45262200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>42890600</v>
+      </c>
+      <c r="F66" s="3">
         <v>32286800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>29400900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>27807900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25757200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>24323000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24108400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>21762000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>20559600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20603200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>20671600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18655800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>18789500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>18361500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>20190100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>18276000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>17935600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15898400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>14939500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>13175300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>12707400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11700700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10222300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>9514400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>9341900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>9484400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1833800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1694800</v>
+      </c>
+      <c r="F72" s="3">
         <v>1609100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1545700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1474000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1388900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1312200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1250300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1197200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1128100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1077400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1007900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>966200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>889600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>837300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>788200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>724200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>682500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>675200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>641000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>585700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>572400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>495000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>458400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>419100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>402100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>374900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>358600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>335200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2522200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2377400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1978800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1777400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1709100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1607800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1542600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1482800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1379100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1329900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1247300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1176600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1070100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1047300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1005600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>953000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>904000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>901400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>860200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>799500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>767500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>688800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>648600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>614900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>594200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>570500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>551800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>526000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F81" s="3">
         <v>63400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>71700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>85100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>76700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>61900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>53100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>69100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>50700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>69500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>41700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>74200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>50700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>47600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>62200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>40500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>33100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>53600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>19000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>75500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>35700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>38400</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>16000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>26700</v>
       </c>
       <c r="AB81" s="3">
         <v>16000</v>
       </c>
       <c r="AC81" s="3">
+        <v>26700</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE81" s="3">
         <v>23000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>17900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7001,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F83" s="3">
         <v>17700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>12400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>14700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>12100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>12200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>12700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>12400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>11600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>12700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>12300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>11700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>11300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>9100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>9700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>8600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>8400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>7200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>4200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>3900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>4400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>3500</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>2900</v>
       </c>
       <c r="AE83" s="3">
         <v>3200</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1261700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3529400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1491200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-154500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-477800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>192600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-622100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>784000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>152400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>371100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>207900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1046700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>266500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2702200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-600200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>744100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>713600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>783800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-118800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>743400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>37200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>502400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>667600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-130000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>462500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>76100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7701,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-16000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-15300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-13600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-16700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-18400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-17400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-12700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-14100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-10300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-11200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-11300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-11900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-17000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-7300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-8600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-17600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-22400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-11100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7982,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-406600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-16200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-21100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-21600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-18700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-18900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-13400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-12700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-10300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-10800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-17800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-11900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-16800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-9000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-10400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-17600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-22800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-226300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7686,11 +8153,11 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8492,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-299800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>918700</v>
+      </c>
+      <c r="F100" s="3">
         <v>14400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-206500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>188200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>113800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-382800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>380100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>76900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-81700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-140000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-36200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>88600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-25400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-131000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-19300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>241500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-35000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-47000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-58100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>104500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-146000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>374200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>127800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-43700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>78600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>79600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-9100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-4600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>6800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-12200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-5700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>8100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>14100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1500</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>300</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1590500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4047100</v>
+      </c>
+      <c r="F102" s="3">
         <v>1500500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-370400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-329600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>294300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1146100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>223400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>263100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>61300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1125600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>223500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2667500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-367500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>697200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>660200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>706700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-23000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>369600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>408400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>621400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>617700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-274800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>518200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>58600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-5500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>45273300</v>
+      </c>
+      <c r="E8" s="3">
         <v>38541900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32287100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34437400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36559300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27613900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30801200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26748600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21830700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19323800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16369100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14817000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15967400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13011600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16381000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18930900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16382700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14341400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11846800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10192100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11244800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9250500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14284900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8243400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20366300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11245000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11279600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7873000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>44490500</v>
+      </c>
+      <c r="E9" s="3">
         <v>37858000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31736800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33980500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36100700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27152300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30376700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26309000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21437200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18930200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15994000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14409100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15593700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12525500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15886800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18440900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15862700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13918400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11481000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9785200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10795000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8890800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13967600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7936200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20029500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11002000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11033500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7632100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>782800</v>
+      </c>
+      <c r="E10" s="3">
         <v>683900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>550300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>456900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>458600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>461600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>424500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>439600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>393500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>393600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>375100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>407900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>373700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>486100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>494200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>490000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>520000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>423000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>365800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>406900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>449800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>359700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>317300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>307200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>336800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>243000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>246100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>240900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>232700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>231700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,79 +1318,82 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-6400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1396,103 +1416,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>12300</v>
       </c>
       <c r="K15" s="3">
         <v>12300</v>
       </c>
       <c r="L15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="M15" s="3">
         <v>11200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>11700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>9100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45032400</v>
+      </c>
+      <c r="E17" s="3">
         <v>38354000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32176700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34349100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36460200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27497500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30701700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26658300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21764200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19226800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16294100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14721800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15897800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12916000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16314600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18860000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16295300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14288900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11841900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10146100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11168500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9223600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14205000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8194400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>20310200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11223300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11245500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7851400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>240900</v>
+      </c>
+      <c r="E18" s="3">
         <v>187900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>110400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>88300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>99100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>116400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>99500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>90300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>97000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>75000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>69600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>66400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>70900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>87400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>52500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>46000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>76300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>79900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>49000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>56100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>21700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>34100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>21600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>30900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,13 +1781,14 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>2700</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1780,17 +1814,17 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1843,103 +1877,109 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E21" s="3">
         <v>212900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>131700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>103200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>114700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>132100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>116800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>102600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>78800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>108200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>86200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>109000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>82700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>108300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>78700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>82600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>98700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>61600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>55700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>84900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>35300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>87100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>53400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>60300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>25600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>25100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>34100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>27300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1979,8 +2019,8 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>227100</v>
+      </c>
+      <c r="E23" s="3">
         <v>184900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>109200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>85600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>97100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>116900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>98100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>88000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>72300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>95700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>75400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>94500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>57500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>95600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>66400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>70900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>87400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>52500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>46000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>76300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>79900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>56100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>34100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>30900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>24400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E24" s="3">
         <v>45900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>16800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E26" s="3">
         <v>139000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>85700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>71700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>85100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>61900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>53100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>69100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>50700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>69500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>41700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>52300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>64000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>41700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>34200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>55300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>77400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>16300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>27200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E27" s="3">
         <v>134400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>61000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>69600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>74100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>59700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>66700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>48900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>67100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>40200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>50700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>47600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>62200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>40500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>53600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>75500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>38400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>16000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2677,8 +2738,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2695,11 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,13 +2955,16 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-2700</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -2920,17 +2990,17 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2983,103 +3053,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E33" s="3">
         <v>139000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>85700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>71700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>85100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>76700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>61900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>53100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>69100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>50700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>69500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>50700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>47600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>62200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>40500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>53600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>75500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>38400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E35" s="3">
         <v>139000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>85700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>71700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>85100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>76700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>61900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>53100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>69100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>50700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>69500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>50700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>47600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>62200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>40500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>53600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>75500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>38400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,145 +3524,149 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2122600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1592700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1605800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1313100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1307300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1398200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1269000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1220800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1305100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1157600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1108300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1401300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1263900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1252100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1108500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1363700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1299700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>983400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1109600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1075600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1001500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1033700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>952600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>465200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>519500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>338900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>471300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>345000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>274400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>358200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35246900</v>
+      </c>
+      <c r="E42" s="3">
         <v>31792000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26943900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22543700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19772700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17674600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16472100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14966300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13680100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12633300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11579700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11534000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10938300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3628,145 +3718,151 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13551700</v>
+      </c>
+      <c r="E43" s="3">
         <v>11329000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14270300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8891400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8643900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8901100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8315600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8470500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9032800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8325800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8157200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8026800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8615600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>603000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>583000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>636800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>626100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>550800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>487700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>634100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>494200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>268300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>428000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>411600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>482600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>333700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>427500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>283800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>305600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>352700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1038800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1373900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>917500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>705400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>796200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>861400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>681100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>587400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>616900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>518400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>537300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>444700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>572100</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3859,48 +3958,48 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>9194900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10109800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9803900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9486400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7888100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7567300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6943200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6464000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5794000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5550100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4541900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4535600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3760400</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3913,50 +4012,53 @@
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51960000</v>
+      </c>
+      <c r="E46" s="3">
         <v>46087600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43737500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33453600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30520100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28835300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26737800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25245000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24997900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22635100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21382500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21406800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21389900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4008,8 +4110,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4049,252 +4154,261 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>7650400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7054200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6563400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8776700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8819200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8763700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7198300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6952300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6020500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5865600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6061300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4853400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5214000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5025800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5141400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>337100</v>
+      </c>
+      <c r="E48" s="3">
         <v>324300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>328500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>310100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>306100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>304800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>300100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>299600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>280600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>264900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>245600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>240500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>235400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>235800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>234700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>223600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>222600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>216900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>218600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>221000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>183200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>172500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>163600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>126600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>76400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>43900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>45700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>45600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>44700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>743800</v>
+      </c>
+      <c r="E49" s="3">
         <v>755000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>736200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>88900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>87000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>80600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>77100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>79500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>80500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>82400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>85200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>88900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>91500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>86200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>90000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>93500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>97200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>100800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>98700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>102500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>106400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>109500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>76300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>73100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>71500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>67900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>65900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>59400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>59300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>555700</v>
+      </c>
+      <c r="E52" s="3">
         <v>590200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>433800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>373700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>316400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>304600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>301500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>266800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>250700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>226900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>182800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>167700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>169200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>41800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>35100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>37000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>39300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>363400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3608400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3763200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53626900</v>
+      </c>
+      <c r="E54" s="3">
         <v>47784400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45268000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34265600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31282900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29585300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27466300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25930800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25651000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23244800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21938700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21933100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21918900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19832400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19859600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19408800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21195700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19229000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18839600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16799800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15799700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13974800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13474900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12389500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10870900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10129300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9936100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10054900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,335 +4968,345 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25339000</v>
+      </c>
+      <c r="E57" s="3">
         <v>20830800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21562300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12038900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11822600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12225500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11597700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11560300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12047200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11034600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10948000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10832000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11239500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9950400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10951400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10914800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10352900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8678800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8754500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7855900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7347000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6450500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6499100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5050100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5145500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4113200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4013200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3963800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20257100</v>
+      </c>
+      <c r="E58" s="3">
         <v>18632500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16697900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15615200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12852700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10989200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10462000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8523500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7912700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7242400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5932200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6529400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>974200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5403500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4385100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3903200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5911600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6838800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6494500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5327900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5514400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4873100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4597400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4990100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3869100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4362400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4233600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4141600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3460300</v>
+      </c>
+      <c r="E59" s="3">
         <v>3994700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2677600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3515400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3614000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3285500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2608900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3266700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2817200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2543700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2837000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2325400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2387400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>171300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>159200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>158900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>169000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>163100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>159800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>168000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>133000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>136900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>141300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>99500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>44800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47000</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>10400</v>
       </c>
       <c r="AD59" s="3">
         <v>10400</v>
       </c>
       <c r="AE59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AF59" s="3">
         <v>11300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49056400</v>
+      </c>
+      <c r="E60" s="3">
         <v>43458000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40939800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31169500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28289300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26500200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24670800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23350500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22778800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20822500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19719100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19688400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14602500</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1764400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1702300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1853900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1104300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1086400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1291900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1077800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>964300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1321400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>930700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>832400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>914800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6069100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>922100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>824200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>847100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>974800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>994700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>755600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>782400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>826900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>887400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>783600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>832700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>459300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>325400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>369900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>507400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>428600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>435400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5363,8 +5509,8 @@
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50927600</v>
+      </c>
+      <c r="E66" s="3">
         <v>45262200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42890600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32286800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29400900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27807900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25757200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24323000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24108400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21762000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20559600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20603200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20671600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18655800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18789500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18361500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20190100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18276000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17935600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15898400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14939500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13175300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12707400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11700700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10222300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9514400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9341900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9484400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2008100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1833800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1694800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1609100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1545700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1474000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1388900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1312200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1250300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1197200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1128100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1077400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1007900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>966200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>889600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>837300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>788200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>724200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>682500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>675200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>641000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>585700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>572400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>495000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>458400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>419100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>402100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>374900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>358600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>335200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2699300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2522200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2377400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1978800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1882000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1777400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1709100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1607800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1542600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1482800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1379100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1329900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1247300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1176600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1070100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1047300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1005600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>953000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>904000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>901400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>860200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>799500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>767500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>688800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>648600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>614900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>594200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>570500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>551800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>526000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E81" s="3">
         <v>139000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>85700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>71700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>85100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>76700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>61900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>53100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>69100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>50700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>69500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>50700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>47600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>62200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>40500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>53600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>75500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>38400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E83" s="3">
         <v>22300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2798600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1261700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3529400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1491200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-154500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-477800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>192600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-622100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>784000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>152400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>371100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>207900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1046700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>266500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2702200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>744100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>713600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>783800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-118800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>743400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>502400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>667600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-130000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>462500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>76100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-17600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-406600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-226300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8159,8 +8393,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-299800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>918700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>14400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-206500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>188200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>113800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-382800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>380100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>76900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-81700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-140000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>88600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-131000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>241500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-35000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-47000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-58100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>104500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-146000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>374200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>127800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-43700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>78600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>79600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>14100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2859700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1590500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4047100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-370400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-329600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>294300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1146100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>223400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>263100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1125600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>223500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2667500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-367500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>697200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>660200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>706700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>369600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>408400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>621400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>617700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-274800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>518200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>58600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5500</v>
       </c>
     </row>
